--- a/Team-Data/2013-14/3-7-2013-14.xlsx
+++ b/Team-Data/2013-14/3-7-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,22 +728,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E2" t="n">
         <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G2" t="n">
-        <v>0.433</v>
+        <v>0.441</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>37.7</v>
+        <v>37.6</v>
       </c>
       <c r="J2" t="n">
         <v>82.2</v>
@@ -685,37 +752,37 @@
         <v>0.458</v>
       </c>
       <c r="L2" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M2" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.374</v>
+        <v>0.377</v>
       </c>
       <c r="O2" t="n">
         <v>16.7</v>
       </c>
       <c r="P2" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.779</v>
+        <v>0.778</v>
       </c>
       <c r="R2" t="n">
         <v>9</v>
       </c>
       <c r="S2" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T2" t="n">
         <v>40.3</v>
       </c>
       <c r="U2" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="V2" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W2" t="n">
         <v>8.5</v>
@@ -727,31 +794,31 @@
         <v>4.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="AA2" t="n">
         <v>19.4</v>
       </c>
       <c r="AB2" t="n">
-        <v>101.4</v>
+        <v>101.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="AD2" t="n">
         <v>27</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG2" t="n">
         <v>18</v>
       </c>
-      <c r="AG2" t="n">
-        <v>19</v>
-      </c>
       <c r="AH2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
@@ -763,16 +830,16 @@
         <v>9</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP2" t="n">
         <v>22</v>
@@ -784,7 +851,7 @@
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>27</v>
@@ -793,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="AV2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
       </c>
       <c r="AX2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -811,7 +878,7 @@
         <v>26</v>
       </c>
       <c r="BB2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC2" t="n">
         <v>16</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F3" t="n">
         <v>41</v>
       </c>
       <c r="G3" t="n">
-        <v>0.339</v>
+        <v>0.328</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>83.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.434</v>
@@ -873,34 +940,34 @@
         <v>19.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.327</v>
+        <v>0.326</v>
       </c>
       <c r="O3" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P3" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R3" t="n">
         <v>11.7</v>
       </c>
       <c r="S3" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="T3" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U3" t="n">
         <v>20.3</v>
       </c>
       <c r="V3" t="n">
-        <v>15.7</v>
+        <v>15.5</v>
       </c>
       <c r="W3" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X3" t="n">
         <v>4.5</v>
@@ -909,7 +976,7 @@
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="AA3" t="n">
         <v>19.2</v>
@@ -918,19 +985,19 @@
         <v>95.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AF3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG3" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AH3" t="n">
         <v>28</v>
@@ -939,13 +1006,13 @@
         <v>25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK3" t="n">
         <v>26</v>
       </c>
       <c r="AL3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM3" t="n">
         <v>22</v>
@@ -954,7 +1021,7 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>25</v>
@@ -966,25 +1033,25 @@
         <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU3" t="n">
         <v>26</v>
       </c>
       <c r="AV3" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AW3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
         <v>19</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -1025,67 +1092,67 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E4" t="n">
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5</v>
+        <v>0.508</v>
       </c>
       <c r="H4" t="n">
         <v>48.4</v>
       </c>
       <c r="I4" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="J4" t="n">
         <v>78.3</v>
       </c>
       <c r="K4" t="n">
-        <v>0.45</v>
+        <v>0.452</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M4" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.359</v>
+        <v>0.364</v>
       </c>
       <c r="O4" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P4" t="n">
         <v>24.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.765</v>
+        <v>0.763</v>
       </c>
       <c r="R4" t="n">
         <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="T4" t="n">
-        <v>38.6</v>
+        <v>38.7</v>
       </c>
       <c r="U4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
         <v>14.5</v>
       </c>
       <c r="W4" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="X4" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
         <v>4.1</v>
@@ -1094,28 +1161,28 @@
         <v>21.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB4" t="n">
-        <v>97.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1.8</v>
+        <v>-1.7</v>
       </c>
       <c r="AD4" t="n">
         <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF4" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG4" t="n">
         <v>15</v>
       </c>
-      <c r="AG4" t="n">
-        <v>16</v>
-      </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>29</v>
@@ -1127,16 +1194,16 @@
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AO4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP4" t="n">
         <v>10</v>
@@ -1145,10 +1212,10 @@
         <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT4" t="n">
         <v>29</v>
@@ -1160,7 +1227,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
         <v>26</v>
@@ -1178,7 +1245,7 @@
         <v>22</v>
       </c>
       <c r="BC4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F5" t="n">
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.468</v>
+        <v>0.459</v>
       </c>
       <c r="H5" t="n">
         <v>48.3</v>
@@ -1228,25 +1295,25 @@
         <v>81.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.439</v>
+        <v>0.438</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="M5" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O5" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.73</v>
+        <v>0.728</v>
       </c>
       <c r="R5" t="n">
         <v>9</v>
@@ -1255,7 +1322,7 @@
         <v>32.8</v>
       </c>
       <c r="T5" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U5" t="n">
         <v>21.1</v>
@@ -1267,10 +1334,10 @@
         <v>6.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z5" t="n">
         <v>18.3</v>
@@ -1282,10 +1349,10 @@
         <v>95.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.6</v>
+        <v>-1.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE5" t="n">
         <v>17</v>
@@ -1309,13 +1376,13 @@
         <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM5" t="n">
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1324,13 +1391,13 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
         <v>22</v>
@@ -1357,10 +1424,10 @@
         <v>9</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E6" t="n">
         <v>34</v>
       </c>
       <c r="F6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>0.548</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I6" t="n">
         <v>34.6</v>
       </c>
       <c r="J6" t="n">
-        <v>80.2</v>
+        <v>80.3</v>
       </c>
       <c r="K6" t="n">
         <v>0.431</v>
@@ -1416,40 +1483,40 @@
         <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.34</v>
+        <v>0.342</v>
       </c>
       <c r="O6" t="n">
         <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R6" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S6" t="n">
         <v>33.1</v>
       </c>
       <c r="T6" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U6" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V6" t="n">
-        <v>15.7</v>
+        <v>15.8</v>
       </c>
       <c r="W6" t="n">
         <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y6" t="n">
         <v>6.2</v>
@@ -1458,19 +1525,19 @@
         <v>19.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>93</v>
+        <v>93.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
@@ -1497,7 +1564,7 @@
         <v>27</v>
       </c>
       <c r="AN6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
         <v>13</v>
@@ -1509,7 +1576,7 @@
         <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>7</v>
@@ -1524,10 +1591,10 @@
         <v>27</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
         <v>29</v>
@@ -1542,7 +1609,7 @@
         <v>30</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7" t="n">
         <v>24</v>
       </c>
       <c r="F7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>0.381</v>
+        <v>0.387</v>
       </c>
       <c r="H7" t="n">
         <v>48.7</v>
@@ -1601,31 +1668,31 @@
         <v>19.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.352</v>
+        <v>0.354</v>
       </c>
       <c r="O7" t="n">
         <v>17.2</v>
       </c>
       <c r="P7" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q7" t="n">
         <v>0.75</v>
       </c>
       <c r="R7" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>44.4</v>
+        <v>44.5</v>
       </c>
       <c r="U7" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V7" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W7" t="n">
         <v>7.1</v>
@@ -1634,7 +1701,7 @@
         <v>3.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z7" t="n">
         <v>20</v>
@@ -1649,10 +1716,10 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
@@ -1667,7 +1734,7 @@
         <v>23</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>30</v>
@@ -1679,7 +1746,7 @@
         <v>20</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1688,7 +1755,7 @@
         <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR7" t="n">
         <v>3</v>
@@ -1715,7 +1782,7 @@
         <v>27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
         <v>21</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8" t="n">
         <v>26</v>
       </c>
       <c r="G8" t="n">
-        <v>0.587</v>
+        <v>0.581</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
@@ -1777,22 +1844,22 @@
         <v>0.473</v>
       </c>
       <c r="L8" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M8" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="N8" t="n">
         <v>0.378</v>
       </c>
       <c r="O8" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P8" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.8</v>
+        <v>0.801</v>
       </c>
       <c r="R8" t="n">
         <v>10</v>
@@ -1804,7 +1871,7 @@
         <v>40.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="V8" t="n">
         <v>13.4</v>
@@ -1816,22 +1883,22 @@
         <v>4.2</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z8" t="n">
         <v>20.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.4</v>
+        <v>104.5</v>
       </c>
       <c r="AC8" t="n">
         <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1846,10 +1913,10 @@
         <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1858,13 +1925,13 @@
         <v>8</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
         <v>26</v>
@@ -1882,7 +1949,7 @@
         <v>28</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
         <v>3</v>
@@ -1891,16 +1958,16 @@
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
         <v>14</v>
       </c>
       <c r="BA8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BB8" t="n">
         <v>7</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -1935,58 +2002,58 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F9" t="n">
         <v>34</v>
       </c>
       <c r="G9" t="n">
-        <v>0.443</v>
+        <v>0.433</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>38.1</v>
+        <v>37.8</v>
       </c>
       <c r="J9" t="n">
-        <v>85.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K9" t="n">
-        <v>0.446</v>
+        <v>0.444</v>
       </c>
       <c r="L9" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M9" t="n">
         <v>23.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.363</v>
+        <v>0.359</v>
       </c>
       <c r="O9" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.717</v>
+        <v>0.719</v>
       </c>
       <c r="R9" t="n">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="S9" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T9" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U9" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="V9" t="n">
         <v>15.6</v>
@@ -2007,46 +2074,46 @@
         <v>21.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.3</v>
+        <v>102.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.2</v>
+        <v>-2.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH9" t="n">
         <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK9" t="n">
         <v>19</v>
       </c>
       <c r="AL9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP9" t="n">
         <v>5</v>
@@ -2058,19 +2125,19 @@
         <v>5</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
@@ -2088,7 +2155,7 @@
         <v>11</v>
       </c>
       <c r="BC9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -2117,25 +2184,25 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E10" t="n">
         <v>24</v>
       </c>
       <c r="F10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
-        <v>0.387</v>
+        <v>0.393</v>
       </c>
       <c r="H10" t="n">
         <v>48.2</v>
       </c>
       <c r="I10" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J10" t="n">
-        <v>86.8</v>
+        <v>86.7</v>
       </c>
       <c r="K10" t="n">
         <v>0.449</v>
@@ -2144,37 +2211,37 @@
         <v>5.8</v>
       </c>
       <c r="M10" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.31</v>
+        <v>0.311</v>
       </c>
       <c r="O10" t="n">
         <v>17.1</v>
       </c>
       <c r="P10" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.67</v>
+        <v>0.669</v>
       </c>
       <c r="R10" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="S10" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T10" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="U10" t="n">
         <v>20.9</v>
       </c>
       <c r="V10" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X10" t="n">
         <v>5.2</v>
@@ -2186,37 +2253,37 @@
         <v>20.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB10" t="n">
         <v>100.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>-2.8</v>
+        <v>-2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH10" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>29</v>
@@ -2243,10 +2310,10 @@
         <v>24</v>
       </c>
       <c r="AT10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV10" t="n">
         <v>16</v>
@@ -2258,19 +2325,19 @@
         <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ10" t="n">
         <v>15</v>
       </c>
       <c r="BA10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB10" t="n">
         <v>15</v>
       </c>
       <c r="BC10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -2299,85 +2366,85 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11" t="n">
         <v>24</v>
       </c>
       <c r="G11" t="n">
-        <v>0.619</v>
+        <v>0.613</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J11" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L11" t="n">
         <v>9.1</v>
       </c>
       <c r="M11" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="N11" t="n">
         <v>0.375</v>
       </c>
       <c r="O11" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P11" t="n">
         <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.747</v>
+        <v>0.746</v>
       </c>
       <c r="R11" t="n">
         <v>11.3</v>
       </c>
       <c r="S11" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="T11" t="n">
         <v>45.7</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V11" t="n">
         <v>15.5</v>
       </c>
       <c r="W11" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X11" t="n">
         <v>5.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
         <v>20</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.4</v>
+        <v>103.3</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2392,16 +2459,16 @@
         <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM11" t="n">
         <v>7</v>
@@ -2410,13 +2477,13 @@
         <v>8</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR11" t="n">
         <v>15</v>
@@ -2425,19 +2492,19 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="n">
         <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2452,7 +2519,7 @@
         <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -2481,22 +2548,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F12" t="n">
         <v>19</v>
       </c>
       <c r="G12" t="n">
-        <v>0.694</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
       </c>
       <c r="I12" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J12" t="n">
         <v>79.5</v>
@@ -2505,64 +2572,64 @@
         <v>0.476</v>
       </c>
       <c r="L12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M12" t="n">
         <v>25.8</v>
       </c>
       <c r="N12" t="n">
-        <v>0.355</v>
+        <v>0.353</v>
       </c>
       <c r="O12" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="P12" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.696</v>
+        <v>0.695</v>
       </c>
       <c r="R12" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S12" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="T12" t="n">
-        <v>45.2</v>
+        <v>45.4</v>
       </c>
       <c r="U12" t="n">
         <v>20.9</v>
       </c>
       <c r="V12" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="W12" t="n">
         <v>7.3</v>
       </c>
       <c r="X12" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y12" t="n">
         <v>5.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AA12" t="n">
         <v>24.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.4</v>
+        <v>106.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AF12" t="n">
         <v>5</v>
@@ -2574,7 +2641,7 @@
         <v>14</v>
       </c>
       <c r="AI12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2583,16 +2650,16 @@
         <v>4</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
@@ -2607,10 +2674,10 @@
         <v>3</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2625,7 +2692,7 @@
         <v>22</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2634,7 +2701,7 @@
         <v>3</v>
       </c>
       <c r="BC12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E13" t="n">
         <v>46</v>
       </c>
       <c r="F13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.742</v>
+        <v>0.754</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
@@ -2681,7 +2748,7 @@
         <v>36.8</v>
       </c>
       <c r="J13" t="n">
-        <v>81.09999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="K13" t="n">
         <v>0.453</v>
@@ -2693,13 +2760,13 @@
         <v>19.3</v>
       </c>
       <c r="N13" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O13" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="P13" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="Q13" t="n">
         <v>0.783</v>
@@ -2708,16 +2775,16 @@
         <v>10.3</v>
       </c>
       <c r="S13" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="T13" t="n">
-        <v>45.2</v>
+        <v>45.4</v>
       </c>
       <c r="U13" t="n">
         <v>20.4</v>
       </c>
       <c r="V13" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W13" t="n">
         <v>7.1</v>
@@ -2732,16 +2799,16 @@
         <v>20.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.7</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2753,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AH13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
         <v>21</v>
@@ -2771,7 +2838,7 @@
         <v>23</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AO13" t="n">
         <v>11</v>
@@ -2789,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU13" t="n">
         <v>25</v>
@@ -2807,7 +2874,7 @@
         <v>14</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
@@ -2816,7 +2883,7 @@
         <v>20</v>
       </c>
       <c r="BC13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -2929,10 +2996,10 @@
         <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH14" t="n">
         <v>23</v>
@@ -2953,22 +3020,22 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR14" t="n">
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>14</v>
@@ -2980,7 +3047,7 @@
         <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX14" t="n">
         <v>18</v>
@@ -2998,7 +3065,7 @@
         <v>1</v>
       </c>
       <c r="BC14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" t="n">
         <v>21</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.339</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J15" t="n">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="K15" t="n">
         <v>0.449</v>
@@ -3057,16 +3124,16 @@
         <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.383</v>
+        <v>0.381</v>
       </c>
       <c r="O15" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="P15" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R15" t="n">
         <v>9.199999999999999</v>
@@ -3075,10 +3142,10 @@
         <v>32.4</v>
       </c>
       <c r="T15" t="n">
-        <v>41.6</v>
+        <v>41.5</v>
       </c>
       <c r="U15" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V15" t="n">
         <v>15.5</v>
@@ -3096,25 +3163,25 @@
         <v>20.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.8</v>
+        <v>101.4</v>
       </c>
       <c r="AC15" t="n">
         <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
       </c>
       <c r="AF15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH15" t="n">
         <v>29</v>
@@ -3123,13 +3190,13 @@
         <v>16</v>
       </c>
       <c r="AJ15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
@@ -3138,13 +3205,13 @@
         <v>3</v>
       </c>
       <c r="AO15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP15" t="n">
         <v>19</v>
       </c>
       <c r="AQ15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3156,10 +3223,10 @@
         <v>23</v>
       </c>
       <c r="AU15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
         <v>26</v>
@@ -3168,16 +3235,16 @@
         <v>3</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA15" t="n">
         <v>28</v>
       </c>
       <c r="BB15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BC15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F16" t="n">
         <v>26</v>
       </c>
       <c r="G16" t="n">
-        <v>0.574</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3227,37 +3294,37 @@
         <v>37.7</v>
       </c>
       <c r="J16" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K16" t="n">
         <v>0.46</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="M16" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="O16" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="P16" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.75</v>
+        <v>0.753</v>
       </c>
       <c r="R16" t="n">
         <v>11.4</v>
       </c>
       <c r="S16" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T16" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="U16" t="n">
         <v>21.7</v>
@@ -3272,22 +3339,22 @@
         <v>4.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA16" t="n">
         <v>18.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.5</v>
+        <v>95.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3338,7 +3405,7 @@
         <v>20</v>
       </c>
       <c r="AU16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
@@ -3347,7 +3414,7 @@
         <v>15</v>
       </c>
       <c r="AX16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
         <v>21</v>
@@ -3359,7 +3426,7 @@
         <v>29</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>5.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
         <v>4</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM17" t="n">
         <v>15</v>
@@ -3535,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA17" t="n">
         <v>13</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E18" t="n">
         <v>12</v>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G18" t="n">
-        <v>0.197</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
         <v>48.6</v>
@@ -3591,31 +3658,31 @@
         <v>35.4</v>
       </c>
       <c r="J18" t="n">
-        <v>82.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="K18" t="n">
         <v>0.429</v>
       </c>
       <c r="L18" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M18" t="n">
         <v>20.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O18" t="n">
         <v>15.8</v>
       </c>
       <c r="P18" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="Q18" t="n">
         <v>0.756</v>
       </c>
       <c r="R18" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S18" t="n">
         <v>29.6</v>
@@ -3627,7 +3694,7 @@
         <v>21.2</v>
       </c>
       <c r="V18" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W18" t="n">
         <v>6.7</v>
@@ -3642,16 +3709,16 @@
         <v>21</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB18" t="n">
-        <v>94</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="AC18" t="n">
         <v>-8.199999999999999</v>
       </c>
       <c r="AD18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>28</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
         <v>29</v>
@@ -3681,7 +3748,7 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO18" t="n">
         <v>27</v>
@@ -3693,16 +3760,16 @@
         <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
       </c>
       <c r="AU18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV18" t="n">
         <v>22</v>
@@ -3711,7 +3778,7 @@
         <v>28</v>
       </c>
       <c r="AX18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY18" t="n">
         <v>19</v>
@@ -3720,7 +3787,7 @@
         <v>18</v>
       </c>
       <c r="BA18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB18" t="n">
         <v>29</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
         <v>30</v>
       </c>
       <c r="G19" t="n">
-        <v>0.508</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3779,19 +3846,19 @@
         <v>0.439</v>
       </c>
       <c r="L19" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="M19" t="n">
         <v>21.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.339</v>
+        <v>0.34</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P19" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="Q19" t="n">
         <v>0.778</v>
@@ -3800,7 +3867,7 @@
         <v>12.9</v>
       </c>
       <c r="S19" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T19" t="n">
         <v>45.7</v>
@@ -3812,10 +3879,10 @@
         <v>13.8</v>
       </c>
       <c r="W19" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y19" t="n">
         <v>5.8</v>
@@ -3827,22 +3894,22 @@
         <v>23.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.3</v>
+        <v>106.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>15</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
         <v>24</v>
@@ -3878,10 +3945,10 @@
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU19" t="n">
         <v>8</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
         <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>0.403</v>
+        <v>0.393</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,49 +4022,49 @@
         <v>37.9</v>
       </c>
       <c r="J20" t="n">
-        <v>83</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
         <v>16</v>
       </c>
       <c r="N20" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="O20" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P20" t="n">
         <v>22.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.766</v>
+        <v>0.764</v>
       </c>
       <c r="R20" t="n">
         <v>11.9</v>
       </c>
       <c r="S20" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T20" t="n">
         <v>42</v>
       </c>
       <c r="U20" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="W20" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X20" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="Y20" t="n">
         <v>6</v>
@@ -4009,13 +4076,13 @@
         <v>19.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2.6</v>
+        <v>-2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4030,7 +4097,7 @@
         <v>14</v>
       </c>
       <c r="AI20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ20" t="n">
         <v>15</v>
@@ -4054,7 +4121,7 @@
         <v>18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR20" t="n">
         <v>9</v>
@@ -4066,13 +4133,13 @@
         <v>21</v>
       </c>
       <c r="AU20" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
         <v>1</v>
@@ -4081,7 +4148,7 @@
         <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA20" t="n">
         <v>20</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F21" t="n">
         <v>40</v>
       </c>
       <c r="G21" t="n">
-        <v>0.365</v>
+        <v>0.355</v>
       </c>
       <c r="H21" t="n">
         <v>48.6</v>
@@ -4140,13 +4207,13 @@
         <v>83.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L21" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="M21" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="N21" t="n">
         <v>0.366</v>
@@ -4158,22 +4225,22 @@
         <v>19.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T21" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U21" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V21" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="W21" t="n">
         <v>7.6</v>
@@ -4185,28 +4252,28 @@
         <v>3.7</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA21" t="n">
         <v>19.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>97.8</v>
+        <v>97.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.4</v>
+        <v>-2.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH21" t="n">
         <v>8</v>
@@ -4236,10 +4303,10 @@
         <v>30</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>27</v>
@@ -4257,7 +4324,7 @@
         <v>16</v>
       </c>
       <c r="AX21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY21" t="n">
         <v>6</v>
@@ -4266,13 +4333,13 @@
         <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB21" t="n">
         <v>21</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -4379,19 +4446,19 @@
         <v>6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
         <v>5</v>
@@ -4409,7 +4476,7 @@
         <v>16</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4427,7 +4494,7 @@
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
         <v>14</v>
@@ -4448,13 +4515,13 @@
         <v>23</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4640,7 @@
         <v>28</v>
       </c>
       <c r="AH23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
@@ -4594,13 +4661,13 @@
         <v>24</v>
       </c>
       <c r="AO23" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
         <v>23</v>
       </c>
       <c r="AQ23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR23" t="n">
         <v>24</v>
@@ -4621,13 +4688,13 @@
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AY23" t="n">
         <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
         <v>12</v>
@@ -4785,7 +4852,7 @@
         <v>28</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>14</v>
@@ -4794,7 +4861,7 @@
         <v>11</v>
       </c>
       <c r="AU24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>2.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AE25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF25" t="n">
         <v>9</v>
@@ -4943,25 +5010,25 @@
         <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK25" t="n">
         <v>7</v>
       </c>
       <c r="AL25" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
         <v>3</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO25" t="n">
         <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
@@ -4976,10 +5043,10 @@
         <v>13</v>
       </c>
       <c r="AU25" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E26" t="n">
         <v>42</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
-        <v>0.677</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>48.3</v>
@@ -5047,28 +5114,28 @@
         <v>39.6</v>
       </c>
       <c r="J26" t="n">
-        <v>87.59999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="K26" t="n">
         <v>0.452</v>
       </c>
       <c r="L26" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="M26" t="n">
         <v>25</v>
       </c>
       <c r="N26" t="n">
-        <v>0.377</v>
+        <v>0.378</v>
       </c>
       <c r="O26" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P26" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.822</v>
+        <v>0.824</v>
       </c>
       <c r="R26" t="n">
         <v>12.6</v>
@@ -5080,10 +5147,10 @@
         <v>46.5</v>
       </c>
       <c r="U26" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V26" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="W26" t="n">
         <v>5.6</v>
@@ -5095,34 +5162,34 @@
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AA26" t="n">
         <v>20.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>107.6</v>
+        <v>107.7</v>
       </c>
       <c r="AC26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF26" t="n">
         <v>5</v>
       </c>
-      <c r="AD26" t="n">
-        <v>8</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>6</v>
-      </c>
       <c r="AG26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH26" t="n">
         <v>14</v>
       </c>
       <c r="AI26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ26" t="n">
         <v>3</v>
@@ -5131,13 +5198,13 @@
         <v>14</v>
       </c>
       <c r="AL26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM26" t="n">
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
@@ -5161,7 +5228,7 @@
         <v>6</v>
       </c>
       <c r="AV26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW26" t="n">
         <v>30</v>
@@ -5170,7 +5237,7 @@
         <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E27" t="n">
         <v>22</v>
       </c>
       <c r="F27" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G27" t="n">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.1</v>
+        <v>37.2</v>
       </c>
       <c r="J27" t="n">
-        <v>82.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K27" t="n">
         <v>0.449</v>
@@ -5241,34 +5308,34 @@
         <v>18.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.341</v>
+        <v>0.342</v>
       </c>
       <c r="O27" t="n">
         <v>20.9</v>
       </c>
       <c r="P27" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.773</v>
+        <v>0.778</v>
       </c>
       <c r="R27" t="n">
         <v>12</v>
       </c>
       <c r="S27" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T27" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U27" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="V27" t="n">
         <v>15.1</v>
       </c>
       <c r="W27" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X27" t="n">
         <v>4</v>
@@ -5280,25 +5347,25 @@
         <v>23</v>
       </c>
       <c r="AA27" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB27" t="n">
-        <v>101.5</v>
+        <v>101.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
         <v>23</v>
       </c>
       <c r="AG27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH27" t="n">
         <v>12</v>
@@ -5313,13 +5380,13 @@
         <v>17</v>
       </c>
       <c r="AL27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM27" t="n">
         <v>25</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO27" t="n">
         <v>4</v>
@@ -5328,7 +5395,7 @@
         <v>4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR27" t="n">
         <v>6</v>
@@ -5340,7 +5407,7 @@
         <v>12</v>
       </c>
       <c r="AU27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV27" t="n">
         <v>18</v>
@@ -5349,7 +5416,7 @@
         <v>18</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY27" t="n">
         <v>24</v>
@@ -5361,10 +5428,10 @@
         <v>4</v>
       </c>
       <c r="BB27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>6.5</v>
       </c>
       <c r="AD28" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
       </c>
       <c r="AF28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
         <v>3</v>
@@ -5525,7 +5592,7 @@
         <v>2</v>
       </c>
       <c r="AV28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW28" t="n">
         <v>17</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F29" t="n">
         <v>26</v>
       </c>
       <c r="G29" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H29" t="n">
         <v>48.7</v>
@@ -5593,37 +5660,37 @@
         <v>36.4</v>
       </c>
       <c r="J29" t="n">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="K29" t="n">
         <v>0.441</v>
       </c>
       <c r="L29" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>22.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.365</v>
+        <v>0.363</v>
       </c>
       <c r="O29" t="n">
         <v>19.1</v>
       </c>
       <c r="P29" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q29" t="n">
         <v>0.776</v>
       </c>
       <c r="R29" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S29" t="n">
         <v>31.3</v>
       </c>
       <c r="T29" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U29" t="n">
         <v>21.4</v>
@@ -5632,16 +5699,16 @@
         <v>14.1</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="X29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="AA29" t="n">
         <v>22</v>
@@ -5650,13 +5717,13 @@
         <v>100.2</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD29" t="n">
         <v>27</v>
       </c>
       <c r="AE29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF29" t="n">
         <v>10</v>
@@ -5671,37 +5738,37 @@
         <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
       </c>
       <c r="AP29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU29" t="n">
         <v>16</v>
@@ -5716,10 +5783,10 @@
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -5757,37 +5824,37 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E30" t="n">
         <v>21</v>
       </c>
       <c r="F30" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G30" t="n">
-        <v>0.339</v>
+        <v>0.344</v>
       </c>
       <c r="H30" t="n">
         <v>48.2</v>
       </c>
       <c r="I30" t="n">
-        <v>35.7</v>
+        <v>35.8</v>
       </c>
       <c r="J30" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K30" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L30" t="n">
         <v>6.8</v>
       </c>
       <c r="M30" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="O30" t="n">
         <v>16.3</v>
@@ -5802,19 +5869,19 @@
         <v>10.9</v>
       </c>
       <c r="S30" t="n">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="T30" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="U30" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="V30" t="n">
         <v>14.6</v>
       </c>
       <c r="W30" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X30" t="n">
         <v>4.7</v>
@@ -5823,25 +5890,25 @@
         <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA30" t="n">
         <v>20.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>94.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC30" t="n">
-        <v>-6.3</v>
+        <v>-6</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
       </c>
       <c r="AF30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG30" t="n">
         <v>25</v>
@@ -5856,25 +5923,25 @@
         <v>26</v>
       </c>
       <c r="AK30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM30" t="n">
         <v>24</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP30" t="n">
         <v>21</v>
       </c>
       <c r="AQ30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR30" t="n">
         <v>19</v>
@@ -5889,7 +5956,7 @@
         <v>28</v>
       </c>
       <c r="AV30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW30" t="n">
         <v>27</v>
@@ -5898,7 +5965,7 @@
         <v>15</v>
       </c>
       <c r="AY30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
@@ -5910,7 +5977,7 @@
         <v>28</v>
       </c>
       <c r="BC30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6038,7 +6105,7 @@
         <v>8</v>
       </c>
       <c r="AK31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL31" t="n">
         <v>15</v>
@@ -6071,7 +6138,7 @@
         <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW31" t="n">
         <v>6</v>
@@ -6092,7 +6159,7 @@
         <v>16</v>
       </c>
       <c r="BC31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-7-2013-14</t>
+          <t>2014-03-07</t>
         </is>
       </c>
     </row>
